--- a/data/trans_dic/IMC_inf_MED_R3-Dificultad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R3-Dificultad-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.3715099916155997</v>
+        <v>0.3487821965129894</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.226348263126446</v>
+        <v>0.2203131186823581</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.3285458242705096</v>
+        <v>0.3185351120913787</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2528496606220801</v>
+        <v>0.2398319077091733</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1531424408090547</v>
+        <v>0.1347675026373799</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.1627782713914452</v>
+        <v>0.1671954295334659</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.3135090558633018</v>
+        <v>0.2959452012047746</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.1917410100191443</v>
+        <v>0.1802502730866636</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.2585473785167386</v>
+        <v>0.2540034594548781</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.3108318907348019</v>
+        <v>0.2936845192925873</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.1797149910590308</v>
+        <v>0.1822903063138955</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.1989767410642577</v>
+        <v>0.1885868037019313</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.2026488167704199</v>
+        <v>0.1920192784884396</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1127876003463152</v>
+        <v>0.1009435537025245</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.07622202617572561</v>
+        <v>0.07732859881039936</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.2766265256807106</v>
+        <v>0.2627811958386003</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1603814322308033</v>
+        <v>0.1522181978786718</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.1681188629109684</v>
+        <v>0.1653989847022795</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.4333214585354222</v>
+        <v>0.4035561939028736</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.2766387773094212</v>
+        <v>0.2673759896103224</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.4846249638997799</v>
+        <v>0.45352400117937</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3107688777098289</v>
+        <v>0.2908054680388175</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1989144872160417</v>
+        <v>0.1755497689612285</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.2981346073540723</v>
+        <v>0.2912670640747617</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.3549583495059646</v>
+        <v>0.3347572530385722</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.2292342804398897</v>
+        <v>0.2098745994398613</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.3462479810050367</v>
+        <v>0.34974586736154</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.2479311857774363</v>
+        <v>0.2313865619339153</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.2154345965422546</v>
+        <v>0.2065341813573121</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.1529663283915139</v>
+        <v>0.1464550628296911</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.228772525295371</v>
+        <v>0.2208141062017267</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1244767918736088</v>
+        <v>0.1168514871682049</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.1218327174608374</v>
+        <v>0.1253740161708091</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.2386062833964921</v>
+        <v>0.2261442842352866</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1706193455928725</v>
+        <v>0.1622557720335867</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.1399040704921548</v>
+        <v>0.1374826404912945</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.1955857012463638</v>
+        <v>0.1848527468663285</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.1627696229585819</v>
+        <v>0.1596126403791711</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.09850868382902699</v>
+        <v>0.09158418875940412</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1739080224826122</v>
+        <v>0.1747715864610003</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.08194796720781918</v>
+        <v>0.07833212668107102</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.07007976884828894</v>
+        <v>0.06875760474576549</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.2000690759740784</v>
+        <v>0.1915738761654472</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.1387986842236549</v>
+        <v>0.133291375995106</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.09777397040497575</v>
+        <v>0.1021069564948177</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.3095830636024574</v>
+        <v>0.2901249458700585</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.2675231963896246</v>
+        <v>0.2629971386407131</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.2316058378167584</v>
+        <v>0.2138586431820632</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.2914629827751415</v>
+        <v>0.2733232165887944</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.174550515522271</v>
+        <v>0.165582797347357</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.2081048180598798</v>
+        <v>0.2119121644132642</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.2779380188084404</v>
+        <v>0.2602440763573992</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.2125779966916898</v>
+        <v>0.1996000164874927</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.1952980517774775</v>
+        <v>0.19074312536887</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.1797075839494679</v>
+        <v>0.1465382090390698</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.1805100778845052</v>
+        <v>0.1676113253013359</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2115551990558072</v>
+        <v>0.2003953669295598</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1751443786092909</v>
+        <v>0.1621950863079638</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1593819648990553</v>
+        <v>0.1447363260017</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.08543671930181672</v>
+        <v>0.08200028338371186</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.1774172711652496</v>
+        <v>0.1542818570681252</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.1700052463770699</v>
+        <v>0.156211909121194</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.1565908485468277</v>
+        <v>0.1491791933333916</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.12779466373227</v>
+        <v>0.1013971024189112</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.1245520537303901</v>
+        <v>0.1172417831671916</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.1437045568220927</v>
+        <v>0.1411479384176006</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1187223321655923</v>
+        <v>0.1174499587749575</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1076330100381735</v>
+        <v>0.100772140106965</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.04518455926907329</v>
+        <v>0.04469060649296772</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.1354176821115135</v>
+        <v>0.1209325252602549</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.1301655420454687</v>
+        <v>0.1192499532971736</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.1185845591475446</v>
+        <v>0.107323525019737</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.250003642842562</v>
+        <v>0.2044777172060235</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.2505531678528206</v>
+        <v>0.2305984876594423</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.284320351305977</v>
+        <v>0.2693809472819437</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.2434869196235969</v>
+        <v>0.2174436214053813</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.2230548691564496</v>
+        <v>0.1956993796328633</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.1455228202992948</v>
+        <v>0.1439428298583852</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.2216195735895155</v>
+        <v>0.1928954306823597</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.2130334644866656</v>
+        <v>0.19418213888041</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.2067903568304355</v>
+        <v>0.1943786852705083</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.2704028371000486</v>
+        <v>0.2615199518274802</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.2208479712333657</v>
+        <v>0.1842341898358911</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.1582076267734154</v>
+        <v>0.1524266951512893</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.1783997243047349</v>
+        <v>0.2023087504741471</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.09477188193758977</v>
+        <v>0.1075283413528506</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.1093153439261548</v>
+        <v>0.1150205333325523</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.2263646630862259</v>
+        <v>0.2338849702836059</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1642608227014273</v>
+        <v>0.1515557362239634</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.1352699426047346</v>
+        <v>0.1348814781920243</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.180775080313934</v>
+        <v>0.1925742258358211</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.1407035948592434</v>
+        <v>0.1251684795948807</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.09250126559029952</v>
+        <v>0.0917448708649537</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.1030508989744468</v>
+        <v>0.1302045794931488</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.04434932033924822</v>
+        <v>0.05760967314529093</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.06020601292693627</v>
+        <v>0.06658621403104997</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1653432101676799</v>
+        <v>0.1738333853129845</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1126166371997194</v>
+        <v>0.1103300888972529</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.0937823783063792</v>
+        <v>0.09245618488355944</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.3649530238787019</v>
+        <v>0.361149944149911</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.3116174150049497</v>
+        <v>0.2656494929928589</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.2516256858376809</v>
+        <v>0.2371551377250419</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.2750254176551273</v>
+        <v>0.2963545446202499</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1819408062103348</v>
+        <v>0.1811869603607239</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.1913999537584541</v>
+        <v>0.1899631752648895</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.2961232474689807</v>
+        <v>0.2969922102135011</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.2266160340280887</v>
+        <v>0.2042474959894231</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.1969452918799198</v>
+        <v>0.1961562052780466</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.278763295473694</v>
+        <v>0.2574167342740283</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.2130158898517304</v>
+        <v>0.2011332831560991</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.1997193371470469</v>
+        <v>0.1916856024640782</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.2189858616577576</v>
+        <v>0.2118436219599846</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.139661037288564</v>
+        <v>0.1287966449128325</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.1121345100919822</v>
+        <v>0.1142574399832456</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.249490398640264</v>
+        <v>0.235166099954575</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1777220344532643</v>
+        <v>0.1666552561871625</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.1615446659536019</v>
+        <v>0.1578466125912172</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.2486008816543207</v>
+        <v>0.2309402517942438</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.183334200837909</v>
+        <v>0.1782417633279202</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1611471622096477</v>
+        <v>0.1507759486113986</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1896765868961637</v>
+        <v>0.1825433812769407</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1153391412167246</v>
+        <v>0.107069822093697</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.07893754140301756</v>
+        <v>0.08456391666551345</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.2279893513555058</v>
+        <v>0.2168801083385214</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.1586063096300076</v>
+        <v>0.1489476781098522</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1349160016619218</v>
+        <v>0.1328407682315238</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3160481245473407</v>
+        <v>0.2895101932324498</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.2435261704347339</v>
+        <v>0.2291786512176086</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.2440745766066508</v>
+        <v>0.2288430935748162</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2518321382999636</v>
+        <v>0.2393150628306941</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1639656505792875</v>
+        <v>0.1528090719662611</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.1486245077730103</v>
+        <v>0.1518392229970069</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.2727535264293153</v>
+        <v>0.2554608400510358</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.1989343369041466</v>
+        <v>0.1852427454441756</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.1898508594071757</v>
+        <v>0.1858984285306031</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1313,31 +1313,31 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -1348,31 +1348,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>64577</v>
+        <v>74256</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44957</v>
+        <v>54271</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>13956</v>
+        <v>14411</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>42025</v>
+        <v>48079</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>27271</v>
+        <v>29242</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5054</v>
+        <v>5623</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>106601</v>
+        <v>122335</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>72228</v>
+        <v>83513</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>19009</v>
+        <v>20034</v>
       </c>
     </row>
     <row r="6">
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>54029</v>
+        <v>62525</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>35694</v>
+        <v>44905</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>8452</v>
+        <v>8532</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>33681</v>
+        <v>38494</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>20085</v>
+        <v>21903</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2366</v>
+        <v>2601</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>94060</v>
+        <v>108626</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>60415</v>
+        <v>70525</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>12361</v>
+        <v>13045</v>
       </c>
     </row>
     <row r="7">
@@ -1418,31 +1418,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>75321</v>
+        <v>85917</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>54945</v>
+        <v>65864</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>20585</v>
+        <v>20518</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>51651</v>
+        <v>58298</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>35422</v>
+        <v>38091</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>9256</v>
+        <v>9796</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>120695</v>
+        <v>138379</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>86352</v>
+        <v>97238</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>25458</v>
+        <v>27585</v>
       </c>
     </row>
     <row r="8">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>40199</v>
+        <v>42220</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>32199</v>
+        <v>35098</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>14033</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>35174</v>
+        <v>39626</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>18069</v>
+        <v>19365</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>8079</v>
+        <v>8902</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>75373</v>
+        <v>81846</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>50268</v>
+        <v>54464</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>22113</v>
+        <v>22935</v>
       </c>
     </row>
     <row r="10">
@@ -1527,31 +1527,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>31712</v>
+        <v>33729</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>24327</v>
+        <v>27125</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>9037</v>
+        <v>8776</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>26738</v>
+        <v>31364</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>11895</v>
+        <v>12982</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>4647</v>
+        <v>4882</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>63200</v>
+        <v>69334</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>40893</v>
+        <v>44741</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>15454</v>
+        <v>17034</v>
       </c>
     </row>
     <row r="11">
@@ -1562,31 +1562,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>50195</v>
+        <v>52937</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>39984</v>
+        <v>44694</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>21248</v>
+        <v>20492</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>44812</v>
+        <v>49049</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>25338</v>
+        <v>27441</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>13800</v>
+        <v>15046</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>87798</v>
+        <v>94187</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>62629</v>
+        <v>66999</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>30868</v>
+        <v>31820</v>
       </c>
     </row>
     <row r="12">
@@ -1601,28 +1601,28 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>31</v>
       </c>
       <c r="F12" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>28</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>26</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>43</v>
@@ -1636,28 +1636,28 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>19195</v>
+        <v>19847</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>19446</v>
+        <v>21170</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>21266</v>
+        <v>21265</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>18851</v>
+        <v>21497</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>16978</v>
+        <v>18159</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>6634</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>38047</v>
+        <v>41343</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>36424</v>
+        <v>39329</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>27899</v>
@@ -1671,31 +1671,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>13650</v>
+        <v>13733</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13418</v>
+        <v>14808</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>14445</v>
+        <v>14978</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>12779</v>
+        <v>15566</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11466</v>
+        <v>12643</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3508</v>
+        <v>3616</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>29040</v>
+        <v>32407</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>27888</v>
+        <v>30023</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>21128</v>
+        <v>20072</v>
       </c>
     </row>
     <row r="15">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>26704</v>
+        <v>27694</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>26992</v>
+        <v>29125</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>28580</v>
+        <v>28586</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>26207</v>
+        <v>28819</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>23761</v>
+        <v>24553</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>11300</v>
+        <v>11645</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>47526</v>
+        <v>51691</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>45643</v>
+        <v>48889</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>36843</v>
+        <v>36353</v>
       </c>
     </row>
     <row r="16">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J16" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="K16" s="6" t="n">
         <v>29</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -1780,31 +1780,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>17518</v>
+        <v>20071</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>13880</v>
+        <v>15356</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>9043</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>10612</v>
+        <v>13589</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>4850</v>
+        <v>6652</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>5522</v>
+        <v>6028</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>28130</v>
+        <v>33660</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>18730</v>
+        <v>22009</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>14565</v>
+        <v>15071</v>
       </c>
     </row>
     <row r="18">
@@ -1815,31 +1815,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>11712</v>
+        <v>14779</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8843</v>
+        <v>10433</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>5287</v>
+        <v>5443</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>6130</v>
+        <v>8746</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>2270</v>
+        <v>3564</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3041</v>
+        <v>3490</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>20547</v>
+        <v>25017</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>12841</v>
+        <v>16022</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>10098</v>
+        <v>10330</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>23644</v>
+        <v>27717</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19585</v>
+        <v>22143</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>14382</v>
+        <v>14069</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>16359</v>
+        <v>19906</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9312</v>
+        <v>11209</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9668</v>
+        <v>9956</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>36799</v>
+        <v>42742</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>25841</v>
+        <v>29661</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>21205</v>
+        <v>21917</v>
       </c>
     </row>
     <row r="20">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -1924,31 +1924,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>141490</v>
+        <v>156393</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>110481</v>
+        <v>125896</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>58297</v>
+        <v>58752</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>106661</v>
+        <v>122790</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>67169</v>
+        <v>73419</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>25289</v>
+        <v>27187</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>248151</v>
+        <v>279183</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>177650</v>
+        <v>199315</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>83586</v>
+        <v>85939</v>
       </c>
     </row>
     <row r="22">
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>126180</v>
+        <v>140307</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>95087</v>
+        <v>111567</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>47038</v>
+        <v>46213</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>92386</v>
+        <v>105807</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>55472</v>
+        <v>61034</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>17802</v>
+        <v>20121</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>226765</v>
+        <v>257475</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>158542</v>
+        <v>178137</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>69808</v>
+        <v>72325</v>
       </c>
     </row>
     <row r="23">
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>160414</v>
+        <v>175891</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>126305</v>
+        <v>143450</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>71244</v>
+        <v>70141</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>122660</v>
+        <v>138713</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>78858</v>
+        <v>87107</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>33518</v>
+        <v>36129</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>271289</v>
+        <v>303277</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>198854</v>
+        <v>221545</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>98232</v>
+        <v>101212</v>
       </c>
     </row>
     <row r="24">
